--- a/02_加值成品/八下/八下3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-1 電解質與導電性　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下3-1 電解質與導電性　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>溶於水能導電的物質是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>濃(離子多)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>變好</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>電解質</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>溶於水不導電的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>非電解質</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>離子</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>不導電</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>食鹽是電解質嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不解離出離子</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>解離出離子</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>糖是電解質嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>非電解質</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>非電解質</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>純水的導電性如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>幾乎不導電</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>非電解質</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>含鹽等電解質</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>極弱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>電解質在水中解離出？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>非電解質</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>離子</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>自由移動離子</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>帶電</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>導電靠的是可移動的？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>溶水測導電</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>離子</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>含鹽等電解質</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>載電</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>酒精溶於水導電嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>鈉鉀等離子</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>濃(離子多)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不導電</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>非電解質</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>溶於水能導電的物質稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不解離出離子</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>電解質</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>食鹽水能導電是因為含？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>離子</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>離子</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-1 電解質與導電性　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下3-1 電解質與導電性　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>食鹽水導電是因為有？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>非電解質</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>自由移動離子</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Na⁺Cl⁻</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>糖水不導電因為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>不解離出離子</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>越好</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>分子</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>固態食鹽為何不導電？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>接電路看燈是否亮</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>自來水(含礦物離子)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>離子不能自由移動</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>可自由移動的離子</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>酸鹼是電解質嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越好</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>可解離</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>離子越多溶液導電性？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>越好</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>溶水測導電</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>載電多</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>熔融食鹽能導電嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>越好</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>離子可動</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>海水比純水導電因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>越好</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>含鹽等電解質</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>非電解質</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>離子多</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>運動飲料補充的電解質指？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>鈉鉀等離子</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>濃(離子多)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>補充</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>酸與鹼在水中是否為電解質？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>越好</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>解離</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>固態離子化合物能導電嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>非電解質</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>離子不能動</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-1 電解質與導電性　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下3-1 電解質與導電性　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何固態食鹽不導電、溶液卻導電？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>固態離子被固定;溶解後可自由移動</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>接電路測燈泡亮度或電流</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>自來水(含礦物離子)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>可自由移動的離子</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>狀態</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>設計實驗比較三杯液體導電性如何做？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>離子不能自由移動</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>接電路測燈泡亮度或電流</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>水含離子易導電</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>海水含較多離子</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>稀鹽酸與濃鹽酸誰導電強？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>濃(離子多)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>自由移動離子</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>濃度</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何潮濕環境觸電更危險？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>離子不能自由移動</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>水含離子易導電</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>自來水(含礦物離子)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>固態離子被固定;溶解後可自由移動</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>風險</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>純水加一點鹽導電性如何變？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>變好</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>增離子</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>判斷未知白色固體是否電解質怎麼做？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>溶水測導電</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不導電</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>檢測</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>熔融氯化鈉導電說明導電需？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>可自由移動的離子</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>水含離子易導電</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>接電路看燈是否亮</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>接電路測燈泡亮度或電流</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>蒸餾水與自來水誰較導電？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>自來水(含礦物離子)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>海水含較多離子</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>可自由移動的離子</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>固態離子被固定;溶解後可自由移動</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>雜質</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>如何用燈泡電路測液體是否電解質？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>接電路測燈泡亮度或電流</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>水含離子易導電</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>離子不能自由移動</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>接電路看燈是否亮</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>檢測</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何海水比蒸餾水容易導電？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>海水含較多離子</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>水含離子易導電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>可自由移動的離子</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>固態離子被固定;溶解後可自由移動</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>離子多</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：這種物質溶到水裡後會拆成帶電的離子，離子能移動幫忙傳電，所以能導電</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>不導電</t>
+          <t>不導電：這種物質溶到水裡並不會拆成離子，沒有帶電粒子可以移動，所以不能導電</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>解離出離子</t>
+          <t>解離出離子：食鹽溶在水中會拆成帶正電的鈉離子和帶負電的氯離子，所以是電解質</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>非電解質</t>
+          <t>非電解質：糖溶在水裡仍然是完整的糖分子，不會拆成離子，所以不能導電</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>極弱</t>
+          <t>極弱：純水裡幾乎沒有能自由移動的離子，所以導電能力非常微弱</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>帶電</t>
+          <t>帶電：電解質溶於水後會拆散成一顆顆帶正電或負電的離子</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>載電</t>
+          <t>載電：溶液要導電，必須要有能夠自由移動的離子在裡面幫忙傳送電荷</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>非電解質</t>
+          <t>非電解質：酒精溶在水中仍然維持完整分子的形態，不會拆成離子，所以不導電</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：溶於水中能解離出可自由移動的離子、使溶液能導電的物質，稱為電解質</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>離子</t>
+          <t>離子：食鹽溶於水後解離成能自由移動的鈉離子和氯離子，這些帶電的離子移動就形成電流，使食鹽水能導電</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Na⁺Cl⁻</t>
+          <t>Na⁺Cl⁻：食鹽溶解後拆成鈉離子和氯離子，這些離子能在水中自由移動，形成電流</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分子</t>
+          <t>分子：糖溶在水裡只是變成一顆顆完整的糖分子分散開來，沒有拆出帶電的離子</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>固定</t>
+          <t>固定：固態食鹽裡的離子雖然帶電，但被緊緊固定在晶體的位置上，無法自由移動傳電</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>可解離</t>
+          <t>可解離：酸和鹼溶於水都會解離出帶電的離子（如氫離子、氫氧根離子），所以都是電解質</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>載電多</t>
+          <t>載電多：溶液中能幫忙傳送電荷的離子數量越多，導電的能力就會越強</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>離子可動</t>
+          <t>離子可動：把固態食鹽加熱融化後，原本固定的離子就能自由移動了，所以能導電</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>離子多</t>
+          <t>離子多：海水裡溶有大量的鹽類等電解質，拆出很多離子，所以導電能力比純水強很多</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>補充</t>
+          <t>補充：運動流汗會流失身體裡的鈉、鉀等離子，運動飲料就是用來補充這些離子</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>解離</t>
+          <t>解離：酸和鹼溶於水中都會解離出離子(如H⁺、OH⁻等)，能使水溶液導電，所以都屬於電解質</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>離子不能動</t>
+          <t>離子不能動：離子化合物在固態時，離子被固定在晶格中無法自由移動，所以固態時不能導電；要溶於水或熔化成液態，離子才能自由移動導電</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>狀態</t>
+          <t>狀態：固態時離子被鎖在晶體的固定位置動不了，一旦溶於水離子就能自由游動起來導電</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：把電極接上電源和燈泡分別放入三杯液體，比較燈泡亮度或電流表數值就能知道導電強弱</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>濃度</t>
+          <t>濃度：濃鹽酸中溶解的離子數量比稀鹽酸多，能幫忙傳電的離子越多，導電能力就越強</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>風險</t>
+          <t>風險：潮濕的水中常溶有各種離子，容易導電，讓電流更容易通過人體造成危險</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>增離子</t>
+          <t>增離子：加入食鹽後水中多了能自由移動的鈉離子和氯離子，導電能力就會明顯提升</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>檢測</t>
+          <t>檢測：把固體溶進水裡，再用電路測試是否能導電，如果能導電就代表它是電解質</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>條件：不管是溶於水還是加熱熔化，只要離子能自由移動，物質就能導電，這是導電的共同條件</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>雜質</t>
+          <t>雜質：自來水中含有礦物質等雜質離子，而蒸餾水幾乎不含離子，所以自來水導電性較強</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>檢測</t>
+          <t>檢測：把待測液體接入含燈泡的電路中，如果液體能導電，電路就會通電使燈泡發亮，可以藉此判斷該液體是否為電解質溶液</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>離子多</t>
+          <t>離子多：海水中溶有大量的鹽類，解離出許多可自由移動的離子；蒸餾水幾乎不含雜質離子，所以海水的導電能力遠比蒸餾水好</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-1_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>濃(離子多)</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>變好</t>
+          <t>鈉鉀等離子</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>幾乎不導電</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>變好</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>離子</t>
+          <t>濃(離子多)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>幾乎不導電</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>不導電</t>
+          <t>電解質</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>不解離出離子</t>
+          <t>濃(離子多)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>幾乎不導電</t>
+          <t>鈉鉀等離子</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>非電解質</t>
+          <t>濃(離子多)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>幾乎不導電</t>
+          <t>溶水測導電</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>電解質</t>
+          <t>能</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>電解質</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>自由移動離子</t>
+          <t>是</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>不導電</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>溶水測導電</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>越好</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>含鹽等電解質</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>鈉鉀等離子</t>
-        </is>
-      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>濃(離子多)</t>
+          <t>能</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>不解離出離子</t>
+          <t>溶水測導電</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>離子</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>鈉鉀等離子</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>幾乎不導電</t>
+          <t>越好</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>電解質</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>非電解質</t>
+          <t>是</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>溶水測導電</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>自由移動離子</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>濃(離子多)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>越好</t>
+          <t>非電解質</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>越好</t>
+          <t>溶水測導電</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>不導電</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>幾乎不導電</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>幾乎不導電</t>
+          <t>電解質</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>不解離出離子</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>越好</t>
+          <t>溶水測導電</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>越好</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>離子</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>濃(離子多)</t>
+          <t>越好</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>電解質</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>電解質</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>越好</t>
+          <t>不導電</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>不解離出離子</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>幾乎不導電</t>
+          <t>濃(離子多)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1399,22 +1399,22 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>電解質</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>溶水測導電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>非電解質</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>電解質</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>不能</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>不導電</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>電解質</t>
+          <t>含鹽等電解質</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>是</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>自由移動離子</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
